--- a/supplement/assets/tkt-software.xlsx
+++ b/supplement/assets/tkt-software.xlsx
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E8" s="176" t="inlineStr">
         <is>
-          <t>Ketua Peneliti (Asisten Ahli)</t>
+          <t>Ketua Peneliti (Lektor)</t>
         </is>
       </c>
       <c r="F8" s="2"/>
